--- a/data/vendor_template_pilot.xlsx
+++ b/data/vendor_template_pilot.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'일일평가'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에러로그'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에러로그'!$A$1:$Q$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1026,7 +1026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1041,10 +1041,11 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="54" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="54" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -1110,20 +1111,25 @@
       </c>
       <c r="M1" s="5" t="inlineStr">
         <is>
+          <t>원인분류</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
           <t>SW버전</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>HW버전</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>상세설명</t>
         </is>
       </c>
-      <c r="P1" s="5" t="inlineStr">
+      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>사진(파일명)</t>
         </is>
@@ -1188,20 +1194,25 @@
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
+          <t>SW</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
           <t>v0.9.1</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="O2" s="6" t="inlineStr">
         <is>
           <t>Rev B</t>
         </is>
       </c>
-      <c r="O2" s="6" t="inlineStr">
+      <c r="P2" s="6" t="inlineStr">
         <is>
           <t>현장 조도 320→210 LUX 급감 구간에서 반복. 노출 보정 후 재현 안 됨. (분석 리포트 별첨)</t>
         </is>
       </c>
-      <c r="P2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="inlineStr">
         <is>
           <t>ERR-001_1.jpg, ERR-001_2.jpg</t>
         </is>
@@ -1266,20 +1277,25 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
+          <t>부품</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
           <t>v0.9.2</t>
         </is>
       </c>
-      <c r="N3" s="6" t="inlineStr">
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>Rev B</t>
         </is>
       </c>
-      <c r="O3" s="6" t="inlineStr">
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>코팅 로트 편차로 마찰계수 0.40→0.28. 압력 상향으로 해결.</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>ERR-002_grip.png</t>
         </is>
@@ -1302,6 +1318,7 @@
       <c r="N4" s="7" t="n"/>
       <c r="O4" s="7" t="n"/>
       <c r="P4" s="7" t="n"/>
+      <c r="Q4" s="7" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="8" t="n"/>
@@ -1320,6 +1337,7 @@
       <c r="N5" s="8" t="n"/>
       <c r="O5" s="8" t="n"/>
       <c r="P5" s="8" t="n"/>
+      <c r="Q5" s="8" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="7" t="n"/>
@@ -1338,6 +1356,7 @@
       <c r="N6" s="7" t="n"/>
       <c r="O6" s="7" t="n"/>
       <c r="P6" s="7" t="n"/>
+      <c r="Q6" s="7" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="8" t="n"/>
@@ -1356,6 +1375,7 @@
       <c r="N7" s="8" t="n"/>
       <c r="O7" s="8" t="n"/>
       <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="7" t="n"/>
@@ -1374,6 +1394,7 @@
       <c r="N8" s="7" t="n"/>
       <c r="O8" s="7" t="n"/>
       <c r="P8" s="7" t="n"/>
+      <c r="Q8" s="7" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="8" t="n"/>
@@ -1392,6 +1413,7 @@
       <c r="N9" s="8" t="n"/>
       <c r="O9" s="8" t="n"/>
       <c r="P9" s="8" t="n"/>
+      <c r="Q9" s="8" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="7" t="n"/>
@@ -1410,6 +1432,7 @@
       <c r="N10" s="7" t="n"/>
       <c r="O10" s="7" t="n"/>
       <c r="P10" s="7" t="n"/>
+      <c r="Q10" s="7" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="8" t="n"/>
@@ -1428,6 +1451,7 @@
       <c r="N11" s="8" t="n"/>
       <c r="O11" s="8" t="n"/>
       <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="7" t="n"/>
@@ -1446,6 +1470,7 @@
       <c r="N12" s="7" t="n"/>
       <c r="O12" s="7" t="n"/>
       <c r="P12" s="7" t="n"/>
+      <c r="Q12" s="7" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="8" t="n"/>
@@ -1464,6 +1489,7 @@
       <c r="N13" s="8" t="n"/>
       <c r="O13" s="8" t="n"/>
       <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="7" t="n"/>
@@ -1482,6 +1508,7 @@
       <c r="N14" s="7" t="n"/>
       <c r="O14" s="7" t="n"/>
       <c r="P14" s="7" t="n"/>
+      <c r="Q14" s="7" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="8" t="n"/>
@@ -1500,6 +1527,7 @@
       <c r="N15" s="8" t="n"/>
       <c r="O15" s="8" t="n"/>
       <c r="P15" s="8" t="n"/>
+      <c r="Q15" s="8" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="7" t="n"/>
@@ -1518,6 +1546,7 @@
       <c r="N16" s="7" t="n"/>
       <c r="O16" s="7" t="n"/>
       <c r="P16" s="7" t="n"/>
+      <c r="Q16" s="7" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="8" t="n"/>
@@ -1536,9 +1565,10 @@
       <c r="N17" s="8" t="n"/>
       <c r="O17" s="8" t="n"/>
       <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P1"/>
+  <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>